--- a/database/controller_excel/Resguardo_Cristobal_Soto_Escalante.xlsx
+++ b/database/controller_excel/Resguardo_Cristobal_Soto_Escalante.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="84">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>05/05/2025</t>
+    <t>02/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -101,7 +101,16 @@
     <t>DVZ-VH-TI-00000</t>
   </si>
   <si>
-    <t>Cargador Laptop</t>
+    <t>Cargador de Laptop</t>
+  </si>
+  <si>
+    <t>Tesla</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
   </si>
   <si>
     <t>LA90PM170</t>
@@ -161,7 +170,7 @@
     <t>9R9J0C3</t>
   </si>
   <si>
-    <t>Cargador Docking</t>
+    <t>Cargador de Docking</t>
   </si>
   <si>
     <t>HA180MP180</t>
@@ -221,6 +230,18 @@
     <t>53QBBH3</t>
   </si>
   <si>
+    <t>ACCESSPOINT</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>dftygihj</t>
+  </si>
+  <si>
+    <t>RTFVYGBUNI</t>
+  </si>
+  <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
   </si>
   <si>
@@ -249,12 +270,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Abraham Palayot Sanchez</t>
-  </si>
-  <si>
-    <t>Informacion Financiera</t>
   </si>
 </sst>
 </file>
@@ -1110,14 +1125,14 @@
         <v>27</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1128,17 +1143,17 @@
         <v>3</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C22" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="38">
-        <v>1929</v>
-      </c>
       <c r="E22" s="38"/>
-      <c r="F22" s="38">
-        <v>730317922522</v>
+      <c r="F22" s="38" t="s">
+        <v>32</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1149,17 +1164,17 @@
         <v>4</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="38" t="s">
         <v>34</v>
       </c>
+      <c r="D23" s="38">
+        <v>1929</v>
+      </c>
       <c r="E23" s="38"/>
-      <c r="F23" s="38" t="s">
-        <v>35</v>
+      <c r="F23" s="38">
+        <v>730317922522</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1170,17 +1185,17 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="D24" s="38" t="s">
         <v>37</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>38</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1191,17 +1206,17 @@
         <v>6</v>
       </c>
       <c r="B25" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="D25" s="38" t="s">
         <v>41</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>42</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1212,10 +1227,10 @@
         <v>7</v>
       </c>
       <c r="B26" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="38" t="s">
         <v>44</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>23</v>
       </c>
       <c r="D26" s="38" t="s">
         <v>45</v>
@@ -1257,14 +1272,14 @@
         <v>50</v>
       </c>
       <c r="C28" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="38" t="s">
         <v>51</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>35</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1275,17 +1290,17 @@
         <v>10</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1296,17 +1311,17 @@
         <v>11</v>
       </c>
       <c r="B30" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="D30" s="38" t="s">
         <v>57</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>58</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1317,17 +1332,17 @@
         <v>12</v>
       </c>
       <c r="B31" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="D31" s="38" t="s">
         <v>61</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>62</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1338,10 +1353,10 @@
         <v>13</v>
       </c>
       <c r="B32" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="38" t="s">
         <v>64</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>23</v>
       </c>
       <c r="D32" s="38" t="s">
         <v>65</v>
@@ -1355,80 +1370,96 @@
       <c r="I32" s="38"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="16"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
+      <c r="A33" s="38">
+        <v>14</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="25"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
+      <c r="A34" s="38">
+        <v>15</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
+      <c r="A36" s="25"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
+      <c r="A37" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
+      <c r="A38" s="27"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="28" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B39" s="28"/>
       <c r="C39" s="28"/>
@@ -1439,23 +1470,22 @@
       <c r="H39" s="28"/>
       <c r="I39" s="28"/>
     </row>
-    <row r="40" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A40" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="1:10" customHeight="1" ht="27">
+    <row r="40" spans="1:10" customHeight="1" ht="15">
+      <c r="A40" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+    </row>
+    <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="28" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B41" s="28"/>
       <c r="C41" s="28"/>
@@ -1466,96 +1496,101 @@
       <c r="H41" s="28"/>
       <c r="I41" s="28"/>
     </row>
-    <row r="42" spans="1:10" customHeight="1" ht="15">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-    </row>
-    <row r="43" spans="1:10" customHeight="1" ht="39">
-      <c r="A43" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
+    <row r="42" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A42" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="2"/>
+    </row>
+    <row r="43" spans="1:10" customHeight="1" ht="27">
+      <c r="A43" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="32"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-    </row>
-    <row r="45" spans="1:10" customHeight="1" ht="15">
-      <c r="A45" s="2"/>
-      <c r="B45" s="32"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+    </row>
+    <row r="45" spans="1:10" customHeight="1" ht="39">
+      <c r="A45" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="32"/>
-      <c r="B46" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="36" t="s">
-        <v>76</v>
-      </c>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="2"/>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
+      <c r="A48" s="32"/>
+      <c r="B48" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
+      <c r="G48" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
+      <c r="D49" s="36" t="s">
+        <v>83</v>
+      </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -1564,68 +1599,90 @@
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="2"/>
-      <c r="B50" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="34" t="str">
+      <c r="G50" s="37"/>
+      <c r="H50" s="37"/>
+      <c r="I50" s="37"/>
+    </row>
+    <row r="51" spans="1:10" customHeight="1" ht="15">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:10" customHeight="1" ht="15">
+      <c r="A52" s="2"/>
+      <c r="B52" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="34" t="str">
         <f>C10</f>
         <v>Cristobal Soto Escalante</v>
       </c>
-      <c r="H50" s="34"/>
-      <c r="I50" s="34"/>
-    </row>
-    <row r="51" spans="1:10" customHeight="1" ht="15">
-      <c r="A51" s="2"/>
-      <c r="B51" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="34" t="str">
+      <c r="H52" s="34"/>
+      <c r="I52" s="34"/>
+    </row>
+    <row r="53" spans="1:10" customHeight="1" ht="15">
+      <c r="A53" s="2"/>
+      <c r="B53" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="34" t="str">
         <f>C12</f>
         <v>Coordinador de Proyectos</v>
       </c>
-      <c r="H51" s="34"/>
-      <c r="I51" s="34"/>
-    </row>
-    <row r="52" spans="1:10" customHeight="1" ht="15">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-    </row>
-    <row r="53" spans="1:10" customHeight="1" ht="15">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15">
-      <c r="A54" s="32"/>
-      <c r="B54" s="32"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+    </row>
+    <row r="55" spans="1:10" customHeight="1" ht="15">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" spans="1:10" customHeight="1" ht="15">
+      <c r="A56" s="32"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1644,23 +1701,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="H35:I35"/>
     <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A38:I38"/>
     <mergeCell ref="A39:I39"/>
     <mergeCell ref="A40:I40"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A42:I42"/>
     <mergeCell ref="A43:I43"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="G46:I46"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="G53:I53"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1703,7 +1760,13 @@
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H19:I32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H19:I34"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Cristobal_Soto_Escalante.xlsx
+++ b/database/controller_excel/Resguardo_Cristobal_Soto_Escalante.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>02/06/2025</t>
+    <t>09/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
